--- a/安全体检报告/风险清单/资产清单.xlsx
+++ b/安全体检报告/风险清单/资产清单.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$V$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -179,250 +182,250 @@
     <t>终端</t>
   </si>
   <si>
+    <t>在线</t>
+  </si>
+  <si>
+    <t>API服务器</t>
+  </si>
+  <si>
+    <t>机房B-02号机柜</t>
+  </si>
+  <si>
+    <t>标签2</t>
+  </si>
+  <si>
+    <t>负责人2</t>
+  </si>
+  <si>
+    <t>13800000001</t>
+  </si>
+  <si>
+    <t>host-srv-001</t>
+  </si>
+  <si>
+    <t>user_001</t>
+  </si>
+  <si>
+    <t>已托管</t>
+  </si>
+  <si>
+    <t>192.168.76.20</t>
+  </si>
+  <si>
+    <t>业务系统3</t>
+  </si>
+  <si>
+    <t>02:06:0E:43:06:61</t>
+  </si>
+  <si>
+    <t>203.102.50.3</t>
+  </si>
+  <si>
+    <t>Windows 10</t>
+  </si>
+  <si>
+    <t>SRV-DB-03</t>
+  </si>
+  <si>
+    <t>暴露</t>
+  </si>
+  <si>
+    <t>数据库服务器</t>
+  </si>
+  <si>
+    <t>机房C-03号机柜</t>
+  </si>
+  <si>
+    <t>标签3</t>
+  </si>
+  <si>
+    <t>STA</t>
+  </si>
+  <si>
+    <t>负责人3</t>
+  </si>
+  <si>
+    <t>13800000002</t>
+  </si>
+  <si>
+    <t>host-srv-002</t>
+  </si>
+  <si>
+    <t>user_002</t>
+  </si>
+  <si>
+    <t>192.168.200.33</t>
+  </si>
+  <si>
+    <t>业务系统4</t>
+  </si>
+  <si>
+    <t>03:09:15:44:09:60</t>
+  </si>
+  <si>
+    <t>203.103.50.4</t>
+  </si>
+  <si>
+    <t>SRV-APP-04</t>
+  </si>
+  <si>
+    <t>应用服务器</t>
+  </si>
+  <si>
+    <t>机房A-04号机柜</t>
+  </si>
+  <si>
+    <t>标签4</t>
+  </si>
+  <si>
+    <t>负责人4</t>
+  </si>
+  <si>
+    <t>13800000003</t>
+  </si>
+  <si>
+    <t>host-srv-003</t>
+  </si>
+  <si>
+    <t>user_003</t>
+  </si>
+  <si>
+    <t>192.168.200.22</t>
+  </si>
+  <si>
+    <t>04:0C:1C:45:0C:5F</t>
+  </si>
+  <si>
+    <t>203.104.50.5</t>
+  </si>
+  <si>
+    <t>SRV-FS-05</t>
+  </si>
+  <si>
+    <t>文件服务器</t>
+  </si>
+  <si>
+    <t>机房B-05号机柜</t>
+  </si>
+  <si>
+    <t>标签5</t>
+  </si>
+  <si>
+    <t>负责人5</t>
+  </si>
+  <si>
+    <t>13800000004</t>
+  </si>
+  <si>
+    <t>host-srv-004</t>
+  </si>
+  <si>
+    <t>user_004</t>
+  </si>
+  <si>
+    <t>192.168.100.205</t>
+  </si>
+  <si>
+    <t>05:0F:23:46:0F:5E</t>
+  </si>
+  <si>
+    <t>203.105.50.6</t>
+  </si>
+  <si>
+    <t>SRV-MAIL-06</t>
+  </si>
+  <si>
+    <t>邮件服务器</t>
+  </si>
+  <si>
+    <t>机房C-06号机柜</t>
+  </si>
+  <si>
+    <t>标签6</t>
+  </si>
+  <si>
+    <t>13800000005</t>
+  </si>
+  <si>
+    <t>host-srv-005</t>
+  </si>
+  <si>
+    <t>user_005</t>
+  </si>
+  <si>
+    <t>192.168.100.200</t>
+  </si>
+  <si>
+    <t>06:12:2A:47:12:5D</t>
+  </si>
+  <si>
+    <t>203.106.50.7</t>
+  </si>
+  <si>
+    <t>SRV-WEB-07</t>
+  </si>
+  <si>
+    <t>终端PC</t>
+  </si>
+  <si>
+    <t>机房A-07号机柜</t>
+  </si>
+  <si>
+    <t>标签7</t>
+  </si>
+  <si>
+    <t>13800000006</t>
+  </si>
+  <si>
+    <t>host-srv-006</t>
+  </si>
+  <si>
+    <t>user_006</t>
+  </si>
+  <si>
+    <t>172.17.75.124</t>
+  </si>
+  <si>
+    <t>07:15:31:48:15:5C</t>
+  </si>
+  <si>
+    <t>203.107.50.8</t>
+  </si>
+  <si>
+    <t>SRV-API-08</t>
+  </si>
+  <si>
+    <t>测试服务器</t>
+  </si>
+  <si>
+    <t>机房B-08号机柜</t>
+  </si>
+  <si>
+    <t>标签8</t>
+  </si>
+  <si>
+    <t>13800000007</t>
+  </si>
+  <si>
+    <t>host-srv-007</t>
+  </si>
+  <si>
+    <t>user_007</t>
+  </si>
+  <si>
+    <t>168.196.23.21</t>
+  </si>
+  <si>
+    <t>08:18:38:49:18:5B</t>
+  </si>
+  <si>
+    <t>203.108.50.9</t>
+  </si>
+  <si>
+    <t>SRV-DB-09</t>
+  </si>
+  <si>
     <t>重要</t>
-  </si>
-  <si>
-    <t>在线</t>
-  </si>
-  <si>
-    <t>API服务器</t>
-  </si>
-  <si>
-    <t>机房B-02号机柜</t>
-  </si>
-  <si>
-    <t>标签2</t>
-  </si>
-  <si>
-    <t>负责人2</t>
-  </si>
-  <si>
-    <t>13800000001</t>
-  </si>
-  <si>
-    <t>host-srv-001</t>
-  </si>
-  <si>
-    <t>user_001</t>
-  </si>
-  <si>
-    <t>已托管</t>
-  </si>
-  <si>
-    <t>192.168.76.20</t>
-  </si>
-  <si>
-    <t>业务系统3</t>
-  </si>
-  <si>
-    <t>02:06:0E:43:06:61</t>
-  </si>
-  <si>
-    <t>203.102.50.3</t>
-  </si>
-  <si>
-    <t>Windows 10</t>
-  </si>
-  <si>
-    <t>SRV-DB-03</t>
-  </si>
-  <si>
-    <t>暴露</t>
-  </si>
-  <si>
-    <t>数据库服务器</t>
-  </si>
-  <si>
-    <t>机房C-03号机柜</t>
-  </si>
-  <si>
-    <t>标签3</t>
-  </si>
-  <si>
-    <t>STA</t>
-  </si>
-  <si>
-    <t>负责人3</t>
-  </si>
-  <si>
-    <t>13800000002</t>
-  </si>
-  <si>
-    <t>host-srv-002</t>
-  </si>
-  <si>
-    <t>user_002</t>
-  </si>
-  <si>
-    <t>192.168.200.33</t>
-  </si>
-  <si>
-    <t>业务系统4</t>
-  </si>
-  <si>
-    <t>03:09:15:44:09:60</t>
-  </si>
-  <si>
-    <t>203.103.50.4</t>
-  </si>
-  <si>
-    <t>SRV-APP-04</t>
-  </si>
-  <si>
-    <t>应用服务器</t>
-  </si>
-  <si>
-    <t>机房A-04号机柜</t>
-  </si>
-  <si>
-    <t>标签4</t>
-  </si>
-  <si>
-    <t>负责人4</t>
-  </si>
-  <si>
-    <t>13800000003</t>
-  </si>
-  <si>
-    <t>host-srv-003</t>
-  </si>
-  <si>
-    <t>user_003</t>
-  </si>
-  <si>
-    <t>192.168.200.22</t>
-  </si>
-  <si>
-    <t>04:0C:1C:45:0C:5F</t>
-  </si>
-  <si>
-    <t>203.104.50.5</t>
-  </si>
-  <si>
-    <t>SRV-FS-05</t>
-  </si>
-  <si>
-    <t>文件服务器</t>
-  </si>
-  <si>
-    <t>机房B-05号机柜</t>
-  </si>
-  <si>
-    <t>标签5</t>
-  </si>
-  <si>
-    <t>负责人5</t>
-  </si>
-  <si>
-    <t>13800000004</t>
-  </si>
-  <si>
-    <t>host-srv-004</t>
-  </si>
-  <si>
-    <t>user_004</t>
-  </si>
-  <si>
-    <t>192.168.100.205</t>
-  </si>
-  <si>
-    <t>05:0F:23:46:0F:5E</t>
-  </si>
-  <si>
-    <t>203.105.50.6</t>
-  </si>
-  <si>
-    <t>SRV-MAIL-06</t>
-  </si>
-  <si>
-    <t>邮件服务器</t>
-  </si>
-  <si>
-    <t>机房C-06号机柜</t>
-  </si>
-  <si>
-    <t>标签6</t>
-  </si>
-  <si>
-    <t>13800000005</t>
-  </si>
-  <si>
-    <t>host-srv-005</t>
-  </si>
-  <si>
-    <t>user_005</t>
-  </si>
-  <si>
-    <t>192.168.100.200</t>
-  </si>
-  <si>
-    <t>06:12:2A:47:12:5D</t>
-  </si>
-  <si>
-    <t>203.106.50.7</t>
-  </si>
-  <si>
-    <t>SRV-WEB-07</t>
-  </si>
-  <si>
-    <t>终端PC</t>
-  </si>
-  <si>
-    <t>机房A-07号机柜</t>
-  </si>
-  <si>
-    <t>标签7</t>
-  </si>
-  <si>
-    <t>13800000006</t>
-  </si>
-  <si>
-    <t>host-srv-006</t>
-  </si>
-  <si>
-    <t>user_006</t>
-  </si>
-  <si>
-    <t>172.17.75.124</t>
-  </si>
-  <si>
-    <t>07:15:31:48:15:5C</t>
-  </si>
-  <si>
-    <t>203.107.50.8</t>
-  </si>
-  <si>
-    <t>SRV-API-08</t>
-  </si>
-  <si>
-    <t>测试服务器</t>
-  </si>
-  <si>
-    <t>机房B-08号机柜</t>
-  </si>
-  <si>
-    <t>标签8</t>
-  </si>
-  <si>
-    <t>13800000007</t>
-  </si>
-  <si>
-    <t>host-srv-007</t>
-  </si>
-  <si>
-    <t>user_007</t>
-  </si>
-  <si>
-    <t>168.196.23.21</t>
-  </si>
-  <si>
-    <t>08:18:38:49:18:5B</t>
-  </si>
-  <si>
-    <t>203.108.50.9</t>
-  </si>
-  <si>
-    <t>SRV-DB-09</t>
   </si>
   <si>
     <t>备份服务器</t>
@@ -783,14 +786,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1246,148 +1242,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1741,6 +1737,12 @@
   <sheetPr/>
   <dimension ref="A1:V21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="16.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="18.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="21.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" t="s">
@@ -1907,10 +1909,10 @@
         <v>49</v>
       </c>
       <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
         <v>50</v>
-      </c>
-      <c r="K3" t="s">
-        <v>51</v>
       </c>
       <c r="L3" t="s">
         <v>33</v>
@@ -1919,134 +1921,134 @@
         <v>31</v>
       </c>
       <c r="N3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" t="s">
         <v>52</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>53</v>
-      </c>
-      <c r="P3" t="s">
-        <v>54</v>
       </c>
       <c r="Q3" t="s">
         <v>37</v>
       </c>
       <c r="R3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S3" t="s">
         <v>55</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>56</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>57</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>58</v>
-      </c>
-      <c r="V3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
       </c>
       <c r="E4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" t="s">
         <v>62</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>63</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>64</v>
-      </c>
-      <c r="H4" t="s">
-        <v>65</v>
       </c>
       <c r="I4" t="s">
         <v>30</v>
       </c>
       <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
         <v>50</v>
       </c>
-      <c r="K4" t="s">
-        <v>51</v>
-      </c>
       <c r="L4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M4" t="s">
         <v>31</v>
       </c>
       <c r="N4" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" t="s">
         <v>67</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>68</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>69</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>70</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>71</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>72</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>73</v>
       </c>
-      <c r="U4" t="s">
-        <v>74</v>
-      </c>
       <c r="V4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
       </c>
       <c r="E5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" t="s">
         <v>77</v>
-      </c>
-      <c r="F5" t="s">
-        <v>78</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s">
         <v>49</v>
       </c>
       <c r="J5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" t="s">
         <v>50</v>
-      </c>
-      <c r="K5" t="s">
-        <v>51</v>
       </c>
       <c r="L5" t="s">
         <v>33</v>
@@ -2055,28 +2057,28 @@
         <v>31</v>
       </c>
       <c r="N5" t="s">
+        <v>79</v>
+      </c>
+      <c r="O5" t="s">
         <v>80</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>81</v>
-      </c>
-      <c r="P5" t="s">
-        <v>82</v>
       </c>
       <c r="Q5" t="s">
         <v>37</v>
       </c>
       <c r="R5" t="s">
+        <v>82</v>
+      </c>
+      <c r="S5" t="s">
         <v>83</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>84</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>85</v>
-      </c>
-      <c r="U5" t="s">
-        <v>86</v>
       </c>
       <c r="V5" t="s">
         <v>42</v>
@@ -2084,7 +2086,7 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -2096,25 +2098,25 @@
         <v>25</v>
       </c>
       <c r="E6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" t="s">
         <v>88</v>
-      </c>
-      <c r="F6" t="s">
-        <v>89</v>
       </c>
       <c r="G6" t="s">
         <v>47</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I6" t="s">
         <v>30</v>
       </c>
       <c r="J6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" t="s">
         <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>51</v>
       </c>
       <c r="L6" t="s">
         <v>33</v>
@@ -2123,36 +2125,36 @@
         <v>31</v>
       </c>
       <c r="N6" t="s">
+        <v>90</v>
+      </c>
+      <c r="O6" t="s">
         <v>91</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>92</v>
-      </c>
-      <c r="P6" t="s">
-        <v>93</v>
       </c>
       <c r="Q6" t="s">
         <v>37</v>
       </c>
       <c r="R6" t="s">
+        <v>93</v>
+      </c>
+      <c r="S6" t="s">
         <v>94</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>95</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>96</v>
       </c>
-      <c r="U6" t="s">
-        <v>97</v>
-      </c>
       <c r="V6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
@@ -2164,22 +2166,22 @@
         <v>25</v>
       </c>
       <c r="E7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" t="s">
         <v>99</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" t="s">
         <v>100</v>
-      </c>
-      <c r="G7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" t="s">
-        <v>101</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="K7" t="s">
         <v>32</v>
@@ -2191,57 +2193,57 @@
         <v>31</v>
       </c>
       <c r="N7" t="s">
+        <v>101</v>
+      </c>
+      <c r="O7" t="s">
         <v>102</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>103</v>
       </c>
-      <c r="P7" t="s">
-        <v>104</v>
-      </c>
       <c r="Q7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R7" t="s">
         <v>38</v>
       </c>
       <c r="S7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T7" t="s">
         <v>105</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>106</v>
       </c>
-      <c r="U7" t="s">
-        <v>107</v>
-      </c>
       <c r="V7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
       </c>
       <c r="E8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" t="s">
         <v>109</v>
-      </c>
-      <c r="F8" t="s">
-        <v>110</v>
       </c>
       <c r="G8" t="s">
         <v>28</v>
       </c>
       <c r="H8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I8" t="s">
         <v>30</v>
@@ -2250,37 +2252,37 @@
         <v>31</v>
       </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M8" t="s">
         <v>31</v>
       </c>
       <c r="N8" t="s">
+        <v>111</v>
+      </c>
+      <c r="O8" t="s">
         <v>112</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>113</v>
-      </c>
-      <c r="P8" t="s">
-        <v>114</v>
       </c>
       <c r="Q8" t="s">
         <v>37</v>
       </c>
       <c r="R8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S8" t="s">
+        <v>114</v>
+      </c>
+      <c r="T8" t="s">
         <v>115</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>116</v>
-      </c>
-      <c r="U8" t="s">
-        <v>117</v>
       </c>
       <c r="V8" t="s">
         <v>42</v>
@@ -2288,37 +2290,37 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
       </c>
       <c r="E9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" t="s">
         <v>119</v>
-      </c>
-      <c r="F9" t="s">
-        <v>120</v>
       </c>
       <c r="G9" t="s">
         <v>47</v>
       </c>
       <c r="H9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
       </c>
       <c r="J9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" t="s">
         <v>50</v>
-      </c>
-      <c r="K9" t="s">
-        <v>51</v>
       </c>
       <c r="L9" t="s">
         <v>33</v>
@@ -2327,36 +2329,36 @@
         <v>31</v>
       </c>
       <c r="N9" t="s">
+        <v>121</v>
+      </c>
+      <c r="O9" t="s">
         <v>122</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>123</v>
-      </c>
-      <c r="P9" t="s">
-        <v>124</v>
       </c>
       <c r="Q9" t="s">
         <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S9" t="s">
+        <v>124</v>
+      </c>
+      <c r="T9" t="s">
         <v>125</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>126</v>
       </c>
-      <c r="U9" t="s">
-        <v>127</v>
-      </c>
       <c r="V9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
@@ -2368,31 +2370,31 @@
         <v>25</v>
       </c>
       <c r="E10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F10" t="s">
         <v>129</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" t="s">
         <v>130</v>
-      </c>
-      <c r="G10" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" t="s">
-        <v>131</v>
       </c>
       <c r="I10" t="s">
         <v>30</v>
       </c>
       <c r="J10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" t="s">
         <v>50</v>
-      </c>
-      <c r="K10" t="s">
-        <v>51</v>
       </c>
       <c r="L10" t="s">
         <v>33</v>
       </c>
       <c r="M10" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="N10" t="s">
         <v>132</v>
@@ -2404,10 +2406,10 @@
         <v>134</v>
       </c>
       <c r="Q10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S10" t="s">
         <v>135</v>
@@ -2419,7 +2421,7 @@
         <v>137</v>
       </c>
       <c r="V10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -2451,16 +2453,16 @@
         <v>49</v>
       </c>
       <c r="J11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" t="s">
         <v>50</v>
-      </c>
-      <c r="K11" t="s">
-        <v>51</v>
       </c>
       <c r="L11" t="s">
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="N11" t="s">
         <v>142</v>
@@ -2475,7 +2477,7 @@
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S11" t="s">
         <v>145</v>
@@ -2498,7 +2500,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -2519,16 +2521,16 @@
         <v>30</v>
       </c>
       <c r="J12" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="K12" t="s">
         <v>32</v>
       </c>
       <c r="L12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="N12" t="s">
         <v>152</v>
@@ -2555,7 +2557,7 @@
         <v>157</v>
       </c>
       <c r="V12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2566,7 +2568,7 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
@@ -2578,7 +2580,7 @@
         <v>160</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H13" t="s">
         <v>161</v>
@@ -2587,16 +2589,16 @@
         <v>49</v>
       </c>
       <c r="J13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" t="s">
         <v>50</v>
-      </c>
-      <c r="K13" t="s">
-        <v>51</v>
       </c>
       <c r="L13" t="s">
         <v>33</v>
       </c>
       <c r="M13" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="N13" t="s">
         <v>162</v>
@@ -2608,10 +2610,10 @@
         <v>164</v>
       </c>
       <c r="Q13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S13" t="s">
         <v>165</v>
@@ -2623,7 +2625,7 @@
         <v>167</v>
       </c>
       <c r="V13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2658,7 +2660,7 @@
         <v>31</v>
       </c>
       <c r="K14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L14" t="s">
         <v>33</v>
@@ -2679,7 +2681,7 @@
         <v>37</v>
       </c>
       <c r="R14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S14" t="s">
         <v>175</v>
@@ -2723,16 +2725,16 @@
         <v>49</v>
       </c>
       <c r="J15" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" t="s">
         <v>50</v>
-      </c>
-      <c r="K15" t="s">
-        <v>51</v>
       </c>
       <c r="L15" t="s">
         <v>33</v>
       </c>
       <c r="M15" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="N15" t="s">
         <v>182</v>
@@ -2747,7 +2749,7 @@
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S15" t="s">
         <v>185</v>
@@ -2759,7 +2761,7 @@
         <v>187</v>
       </c>
       <c r="V15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2770,7 +2772,7 @@
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
         <v>25</v>
@@ -2782,7 +2784,7 @@
         <v>190</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
         <v>191</v>
@@ -2791,16 +2793,16 @@
         <v>30</v>
       </c>
       <c r="J16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" t="s">
         <v>50</v>
       </c>
-      <c r="K16" t="s">
-        <v>51</v>
-      </c>
       <c r="L16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M16" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="N16" t="s">
         <v>192</v>
@@ -2812,10 +2814,10 @@
         <v>194</v>
       </c>
       <c r="Q16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S16" t="s">
         <v>195</v>
@@ -2827,7 +2829,7 @@
         <v>197</v>
       </c>
       <c r="V16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2838,7 +2840,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
@@ -2859,7 +2861,7 @@
         <v>49</v>
       </c>
       <c r="J17" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="K17" t="s">
         <v>32</v>
@@ -2868,7 +2870,7 @@
         <v>33</v>
       </c>
       <c r="M17" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="N17" t="s">
         <v>202</v>
@@ -2927,16 +2929,16 @@
         <v>30</v>
       </c>
       <c r="J18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" t="s">
         <v>50</v>
-      </c>
-      <c r="K18" t="s">
-        <v>51</v>
       </c>
       <c r="L18" t="s">
         <v>33</v>
       </c>
       <c r="M18" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="N18" t="s">
         <v>212</v>
@@ -2951,7 +2953,7 @@
         <v>37</v>
       </c>
       <c r="R18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S18" t="s">
         <v>215</v>
@@ -2963,7 +2965,7 @@
         <v>217</v>
       </c>
       <c r="V18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2986,7 +2988,7 @@
         <v>220</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H19" t="s">
         <v>221</v>
@@ -2995,16 +2997,16 @@
         <v>49</v>
       </c>
       <c r="J19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" t="s">
         <v>50</v>
-      </c>
-      <c r="K19" t="s">
-        <v>51</v>
       </c>
       <c r="L19" t="s">
         <v>33</v>
       </c>
       <c r="M19" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="N19" t="s">
         <v>222</v>
@@ -3016,10 +3018,10 @@
         <v>224</v>
       </c>
       <c r="Q19" t="s">
+        <v>69</v>
+      </c>
+      <c r="R19" t="s">
         <v>70</v>
-      </c>
-      <c r="R19" t="s">
-        <v>71</v>
       </c>
       <c r="S19" t="s">
         <v>225</v>
@@ -3031,7 +3033,7 @@
         <v>227</v>
       </c>
       <c r="V19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3042,7 +3044,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
         <v>25</v>
@@ -3066,10 +3068,10 @@
         <v>31</v>
       </c>
       <c r="K20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M20" t="s">
         <v>31</v>
@@ -3087,7 +3089,7 @@
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S20" t="s">
         <v>235</v>
@@ -3110,7 +3112,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
@@ -3131,16 +3133,16 @@
         <v>49</v>
       </c>
       <c r="J21" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" t="s">
         <v>50</v>
-      </c>
-      <c r="K21" t="s">
-        <v>51</v>
       </c>
       <c r="L21" t="s">
         <v>33</v>
       </c>
       <c r="M21" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="N21" t="s">
         <v>242</v>
@@ -3155,7 +3157,7 @@
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S21" t="s">
         <v>245</v>
@@ -3167,10 +3169,13 @@
         <v>247</v>
       </c>
       <c r="V21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:V21">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/安全体检报告/风险清单/资产清单.xlsx
+++ b/安全体检报告/风险清单/资产清单.xlsx
@@ -9,9 +9,6 @@
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$V$21</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="253">
   <si>
     <t>IP地址</t>
   </si>
@@ -98,6 +95,9 @@
     <t>托管状态</t>
   </si>
   <si>
+    <t>数据源</t>
+  </si>
+  <si>
     <t>10.248.38.136</t>
   </si>
   <si>
@@ -158,7 +158,10 @@
     <t>user_000</t>
   </si>
   <si>
-    <t>未托管</t>
+    <t>已托管</t>
+  </si>
+  <si>
+    <t>EDR（EDR_LYM）</t>
   </si>
   <si>
     <t>192.168.213.156</t>
@@ -182,6 +185,9 @@
     <t>终端</t>
   </si>
   <si>
+    <t>重要</t>
+  </si>
+  <si>
     <t>在线</t>
   </si>
   <si>
@@ -206,9 +212,6 @@
     <t>user_001</t>
   </si>
   <si>
-    <t>已托管</t>
-  </si>
-  <si>
     <t>192.168.76.20</t>
   </si>
   <si>
@@ -293,6 +296,9 @@
     <t>192.168.200.22</t>
   </si>
   <si>
+    <t>业务系统5</t>
+  </si>
+  <si>
     <t>04:0C:1C:45:0C:5F</t>
   </si>
   <si>
@@ -326,6 +332,9 @@
     <t>192.168.100.205</t>
   </si>
   <si>
+    <t>业务系统6</t>
+  </si>
+  <si>
     <t>05:0F:23:46:0F:5E</t>
   </si>
   <si>
@@ -425,9 +434,6 @@
     <t>SRV-DB-09</t>
   </si>
   <si>
-    <t>重要</t>
-  </si>
-  <si>
     <t>备份服务器</t>
   </si>
   <si>
@@ -719,6 +725,9 @@
     <t>172.16.88.30</t>
   </si>
   <si>
+    <t>业务系统7</t>
+  </si>
+  <si>
     <t>12:36:7E:53:36:51</t>
   </si>
   <si>
@@ -747,6 +756,9 @@
   </si>
   <si>
     <t>192.168.1.100</t>
+  </si>
+  <si>
+    <t>业务系统8</t>
   </si>
   <si>
     <t>13:39:85:54:39:50</t>
@@ -1387,8 +1399,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1735,1447 +1748,1506 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A2:W22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.8888888888889" customWidth="1"/>
-    <col min="3" max="3" width="18.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="21.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="1" max="1" width="26.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="13.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="20.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" t="s">
+    <row r="2" spans="1:23">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V2" t="s">
         <v>21</v>
       </c>
+      <c r="W2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:22">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:23">
+      <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G3" t="s">
         <v>29</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H3" t="s">
         <v>30</v>
       </c>
-      <c r="J2" t="s">
+      <c r="I3" t="s">
         <v>31</v>
       </c>
-      <c r="K2" t="s">
+      <c r="J3" t="s">
         <v>32</v>
       </c>
-      <c r="L2" t="s">
+      <c r="K3" t="s">
         <v>33</v>
       </c>
-      <c r="M2" t="s">
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" t="s">
+        <v>41</v>
+      </c>
+      <c r="U3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S4" t="s">
+        <v>58</v>
+      </c>
+      <c r="T4" t="s">
+        <v>59</v>
+      </c>
+      <c r="U4" t="s">
+        <v>60</v>
+      </c>
+      <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="N2" t="s">
+      <c r="J5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" t="s">
+        <v>69</v>
+      </c>
+      <c r="P5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>71</v>
+      </c>
+      <c r="R5" t="s">
+        <v>72</v>
+      </c>
+      <c r="S5" t="s">
+        <v>73</v>
+      </c>
+      <c r="T5" t="s">
+        <v>74</v>
+      </c>
+      <c r="U5" t="s">
+        <v>75</v>
+      </c>
+      <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" t="s">
         <v>34</v>
       </c>
-      <c r="O2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q6" t="s">
         <v>38</v>
       </c>
-      <c r="S2" t="s">
+      <c r="R6" t="s">
+        <v>84</v>
+      </c>
+      <c r="S6" t="s">
+        <v>85</v>
+      </c>
+      <c r="T6" t="s">
+        <v>86</v>
+      </c>
+      <c r="U6" t="s">
+        <v>87</v>
+      </c>
+      <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>92</v>
+      </c>
+      <c r="I7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" t="s">
+        <v>93</v>
+      </c>
+      <c r="O7" t="s">
+        <v>94</v>
+      </c>
+      <c r="P7" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" t="s">
+        <v>96</v>
+      </c>
+      <c r="S7" t="s">
+        <v>97</v>
+      </c>
+      <c r="T7" t="s">
+        <v>98</v>
+      </c>
+      <c r="U7" t="s">
+        <v>99</v>
+      </c>
+      <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" t="s">
+        <v>105</v>
+      </c>
+      <c r="O8" t="s">
+        <v>106</v>
+      </c>
+      <c r="P8" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>71</v>
+      </c>
+      <c r="R8" t="s">
         <v>39</v>
       </c>
-      <c r="T2" t="s">
-        <v>40</v>
-      </c>
-      <c r="U2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V2" t="s">
-        <v>42</v>
+      <c r="S8" t="s">
+        <v>108</v>
+      </c>
+      <c r="T8" t="s">
+        <v>109</v>
+      </c>
+      <c r="U8" t="s">
+        <v>110</v>
+      </c>
+      <c r="V8" t="s">
+        <v>43</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
-      <c r="A3" t="s">
+    <row r="9" spans="1:23">
+      <c r="A9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" t="s">
+        <v>115</v>
+      </c>
+      <c r="O9" t="s">
+        <v>116</v>
+      </c>
+      <c r="P9" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R9" t="s">
+        <v>57</v>
+      </c>
+      <c r="S9" t="s">
+        <v>118</v>
+      </c>
+      <c r="T9" t="s">
+        <v>119</v>
+      </c>
+      <c r="U9" t="s">
+        <v>120</v>
+      </c>
+      <c r="V9" t="s">
         <v>43</v>
       </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="W9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" t="s">
+        <v>125</v>
+      </c>
+      <c r="O10" t="s">
+        <v>126</v>
+      </c>
+      <c r="P10" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>38</v>
+      </c>
+      <c r="R10" t="s">
+        <v>72</v>
+      </c>
+      <c r="S10" t="s">
+        <v>128</v>
+      </c>
+      <c r="T10" t="s">
+        <v>129</v>
+      </c>
+      <c r="U10" t="s">
+        <v>130</v>
+      </c>
+      <c r="V10" t="s">
+        <v>43</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" t="s">
+        <v>135</v>
+      </c>
+      <c r="O11" t="s">
+        <v>136</v>
+      </c>
+      <c r="P11" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" t="s">
+        <v>84</v>
+      </c>
+      <c r="S11" t="s">
+        <v>138</v>
+      </c>
+      <c r="T11" t="s">
+        <v>139</v>
+      </c>
+      <c r="U11" t="s">
+        <v>140</v>
+      </c>
+      <c r="V11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>144</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" t="s">
+        <v>52</v>
+      </c>
+      <c r="N12" t="s">
+        <v>145</v>
+      </c>
+      <c r="O12" t="s">
+        <v>146</v>
+      </c>
+      <c r="P12" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>38</v>
+      </c>
+      <c r="R12" t="s">
+        <v>96</v>
+      </c>
+      <c r="S12" t="s">
+        <v>148</v>
+      </c>
+      <c r="T12" t="s">
+        <v>149</v>
+      </c>
+      <c r="U12" t="s">
+        <v>150</v>
+      </c>
+      <c r="V12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F13" t="s">
+        <v>153</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N13" t="s">
+        <v>155</v>
+      </c>
+      <c r="O13" t="s">
+        <v>156</v>
+      </c>
+      <c r="P13" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S13" t="s">
+        <v>158</v>
+      </c>
+      <c r="T13" t="s">
+        <v>159</v>
+      </c>
+      <c r="U13" t="s">
+        <v>160</v>
+      </c>
+      <c r="V13" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" t="s">
+        <v>163</v>
+      </c>
+      <c r="G14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" t="s">
+        <v>164</v>
+      </c>
+      <c r="I14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14" t="s">
+        <v>165</v>
+      </c>
+      <c r="O14" t="s">
+        <v>166</v>
+      </c>
+      <c r="P14" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>71</v>
+      </c>
+      <c r="R14" t="s">
+        <v>57</v>
+      </c>
+      <c r="S14" t="s">
+        <v>168</v>
+      </c>
+      <c r="T14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U14" t="s">
+        <v>170</v>
+      </c>
+      <c r="V14" t="s">
+        <v>43</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>172</v>
+      </c>
+      <c r="F15" t="s">
+        <v>173</v>
+      </c>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>174</v>
+      </c>
+      <c r="I15" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" t="s">
+        <v>175</v>
+      </c>
+      <c r="O15" t="s">
+        <v>176</v>
+      </c>
+      <c r="P15" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R15" t="s">
+        <v>72</v>
+      </c>
+      <c r="S15" t="s">
+        <v>178</v>
+      </c>
+      <c r="T15" t="s">
+        <v>179</v>
+      </c>
+      <c r="U15" t="s">
+        <v>180</v>
+      </c>
+      <c r="V15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
         <v>46</v>
       </c>
-      <c r="G3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>182</v>
+      </c>
+      <c r="F16" t="s">
+        <v>183</v>
+      </c>
+      <c r="G16" t="s">
         <v>49</v>
       </c>
-      <c r="J3" t="s">
+      <c r="H16" t="s">
+        <v>184</v>
+      </c>
+      <c r="I16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" t="s">
+        <v>34</v>
+      </c>
+      <c r="M16" t="s">
+        <v>52</v>
+      </c>
+      <c r="N16" t="s">
+        <v>185</v>
+      </c>
+      <c r="O16" t="s">
+        <v>186</v>
+      </c>
+      <c r="P16" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>38</v>
+      </c>
+      <c r="R16" t="s">
+        <v>84</v>
+      </c>
+      <c r="S16" t="s">
+        <v>188</v>
+      </c>
+      <c r="T16" t="s">
+        <v>189</v>
+      </c>
+      <c r="U16" t="s">
+        <v>190</v>
+      </c>
+      <c r="V16" t="s">
+        <v>43</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17" t="s">
+        <v>191</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>192</v>
+      </c>
+      <c r="F17" t="s">
+        <v>193</v>
+      </c>
+      <c r="G17" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" t="s">
+        <v>194</v>
+      </c>
+      <c r="I17" t="s">
         <v>31</v>
       </c>
-      <c r="K3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="J17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17" t="s">
+        <v>52</v>
+      </c>
+      <c r="N17" t="s">
+        <v>195</v>
+      </c>
+      <c r="O17" t="s">
+        <v>196</v>
+      </c>
+      <c r="P17" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>71</v>
+      </c>
+      <c r="R17" t="s">
+        <v>96</v>
+      </c>
+      <c r="S17" t="s">
+        <v>198</v>
+      </c>
+      <c r="T17" t="s">
+        <v>199</v>
+      </c>
+      <c r="U17" t="s">
+        <v>200</v>
+      </c>
+      <c r="V17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F18" t="s">
+        <v>203</v>
+      </c>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
+        <v>204</v>
+      </c>
+      <c r="I18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" t="s">
         <v>33</v>
       </c>
-      <c r="M3" t="s">
+      <c r="L18" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" t="s">
+        <v>52</v>
+      </c>
+      <c r="N18" t="s">
+        <v>205</v>
+      </c>
+      <c r="O18" t="s">
+        <v>206</v>
+      </c>
+      <c r="P18" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>38</v>
+      </c>
+      <c r="R18" t="s">
+        <v>39</v>
+      </c>
+      <c r="S18" t="s">
+        <v>208</v>
+      </c>
+      <c r="T18" t="s">
+        <v>209</v>
+      </c>
+      <c r="U18" t="s">
+        <v>210</v>
+      </c>
+      <c r="V18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>212</v>
+      </c>
+      <c r="F19" t="s">
+        <v>213</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" t="s">
+        <v>214</v>
+      </c>
+      <c r="I19" t="s">
         <v>31</v>
       </c>
-      <c r="N3" t="s">
+      <c r="J19" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" t="s">
+        <v>34</v>
+      </c>
+      <c r="M19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" t="s">
+        <v>215</v>
+      </c>
+      <c r="O19" t="s">
+        <v>216</v>
+      </c>
+      <c r="P19" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>38</v>
+      </c>
+      <c r="R19" t="s">
+        <v>57</v>
+      </c>
+      <c r="S19" t="s">
+        <v>218</v>
+      </c>
+      <c r="T19" t="s">
+        <v>219</v>
+      </c>
+      <c r="U19" t="s">
+        <v>220</v>
+      </c>
+      <c r="V19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>222</v>
+      </c>
+      <c r="F20" t="s">
+        <v>223</v>
+      </c>
+      <c r="G20" t="s">
+        <v>65</v>
+      </c>
+      <c r="H20" t="s">
+        <v>224</v>
+      </c>
+      <c r="I20" t="s">
         <v>51</v>
       </c>
-      <c r="O3" t="s">
+      <c r="J20" t="s">
         <v>52</v>
       </c>
-      <c r="P3" t="s">
+      <c r="K20" t="s">
         <v>53</v>
       </c>
-      <c r="Q3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" t="s">
-        <v>54</v>
-      </c>
-      <c r="S3" t="s">
-        <v>55</v>
-      </c>
-      <c r="T3" t="s">
-        <v>56</v>
-      </c>
-      <c r="U3" t="s">
-        <v>57</v>
-      </c>
-      <c r="V3" t="s">
-        <v>58</v>
+      <c r="L20" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" t="s">
+        <v>52</v>
+      </c>
+      <c r="N20" t="s">
+        <v>225</v>
+      </c>
+      <c r="O20" t="s">
+        <v>226</v>
+      </c>
+      <c r="P20" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>71</v>
+      </c>
+      <c r="R20" t="s">
+        <v>72</v>
+      </c>
+      <c r="S20" t="s">
+        <v>228</v>
+      </c>
+      <c r="T20" t="s">
+        <v>229</v>
+      </c>
+      <c r="U20" t="s">
+        <v>230</v>
+      </c>
+      <c r="V20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
-      <c r="A4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" t="s">
+    <row r="21" spans="1:23">
+      <c r="A21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>232</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" t="s">
+        <v>233</v>
+      </c>
+      <c r="F21" t="s">
+        <v>234</v>
+      </c>
+      <c r="G21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" t="s">
+        <v>235</v>
+      </c>
+      <c r="I21" t="s">
         <v>31</v>
       </c>
-      <c r="K4" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" t="s">
-        <v>65</v>
-      </c>
-      <c r="M4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" t="s">
-        <v>66</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" t="s">
         <v>67</v>
       </c>
-      <c r="P4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>69</v>
-      </c>
-      <c r="R4" t="s">
-        <v>70</v>
-      </c>
-      <c r="S4" t="s">
-        <v>71</v>
-      </c>
-      <c r="T4" t="s">
-        <v>72</v>
-      </c>
-      <c r="U4" t="s">
-        <v>73</v>
-      </c>
-      <c r="V4" t="s">
-        <v>58</v>
+      <c r="M21" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" t="s">
+        <v>236</v>
+      </c>
+      <c r="O21" t="s">
+        <v>237</v>
+      </c>
+      <c r="P21" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>38</v>
+      </c>
+      <c r="R21" t="s">
+        <v>84</v>
+      </c>
+      <c r="S21" t="s">
+        <v>239</v>
+      </c>
+      <c r="T21" t="s">
+        <v>240</v>
+      </c>
+      <c r="U21" t="s">
+        <v>241</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I5" t="s">
+    <row r="22" spans="1:23">
+      <c r="A22" t="s">
+        <v>242</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>243</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" t="s">
+        <v>244</v>
+      </c>
+      <c r="F22" t="s">
+        <v>245</v>
+      </c>
+      <c r="G22" t="s">
         <v>49</v>
       </c>
-      <c r="J5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" t="s">
-        <v>80</v>
-      </c>
-      <c r="P5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" t="s">
-        <v>82</v>
-      </c>
-      <c r="S5" t="s">
-        <v>83</v>
-      </c>
-      <c r="T5" t="s">
-        <v>84</v>
-      </c>
-      <c r="U5" t="s">
-        <v>85</v>
-      </c>
-      <c r="V5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
-      <c r="A6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" t="s">
-        <v>90</v>
-      </c>
-      <c r="O6" t="s">
-        <v>91</v>
-      </c>
-      <c r="P6" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R6" t="s">
-        <v>93</v>
-      </c>
-      <c r="S6" t="s">
-        <v>94</v>
-      </c>
-      <c r="T6" t="s">
-        <v>95</v>
-      </c>
-      <c r="U6" t="s">
+      <c r="H22" t="s">
+        <v>246</v>
+      </c>
+      <c r="I22" t="s">
+        <v>51</v>
+      </c>
+      <c r="J22" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M22" t="s">
+        <v>52</v>
+      </c>
+      <c r="N22" t="s">
+        <v>247</v>
+      </c>
+      <c r="O22" t="s">
+        <v>248</v>
+      </c>
+      <c r="P22" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R22" t="s">
         <v>96</v>
       </c>
-      <c r="V6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
-      <c r="A7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="S22" t="s">
+        <v>250</v>
+      </c>
+      <c r="T22" t="s">
+        <v>251</v>
+      </c>
+      <c r="U22" t="s">
+        <v>252</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" t="s">
-        <v>100</v>
-      </c>
-      <c r="I7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" t="s">
-        <v>101</v>
-      </c>
-      <c r="O7" t="s">
-        <v>102</v>
-      </c>
-      <c r="P7" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>69</v>
-      </c>
-      <c r="R7" t="s">
-        <v>38</v>
-      </c>
-      <c r="S7" t="s">
-        <v>104</v>
-      </c>
-      <c r="T7" t="s">
-        <v>105</v>
-      </c>
-      <c r="U7" t="s">
-        <v>106</v>
-      </c>
-      <c r="V7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" t="s">
-        <v>110</v>
-      </c>
-      <c r="I8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" t="s">
-        <v>111</v>
-      </c>
-      <c r="O8" t="s">
-        <v>112</v>
-      </c>
-      <c r="P8" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>37</v>
-      </c>
-      <c r="R8" t="s">
-        <v>54</v>
-      </c>
-      <c r="S8" t="s">
-        <v>114</v>
-      </c>
-      <c r="T8" t="s">
-        <v>115</v>
-      </c>
-      <c r="U8" t="s">
-        <v>116</v>
-      </c>
-      <c r="V8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9" t="s">
-        <v>121</v>
-      </c>
-      <c r="O9" t="s">
-        <v>122</v>
-      </c>
-      <c r="P9" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>37</v>
-      </c>
-      <c r="R9" t="s">
-        <v>70</v>
-      </c>
-      <c r="S9" t="s">
-        <v>124</v>
-      </c>
-      <c r="T9" t="s">
-        <v>125</v>
-      </c>
-      <c r="U9" t="s">
-        <v>126</v>
-      </c>
-      <c r="V9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>128</v>
-      </c>
-      <c r="F10" t="s">
-        <v>129</v>
-      </c>
-      <c r="G10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" t="s">
-        <v>130</v>
-      </c>
-      <c r="I10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10" t="s">
-        <v>33</v>
-      </c>
-      <c r="M10" t="s">
-        <v>131</v>
-      </c>
-      <c r="N10" t="s">
-        <v>132</v>
-      </c>
-      <c r="O10" t="s">
-        <v>133</v>
-      </c>
-      <c r="P10" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R10" t="s">
-        <v>82</v>
-      </c>
-      <c r="S10" t="s">
-        <v>135</v>
-      </c>
-      <c r="T10" t="s">
-        <v>136</v>
-      </c>
-      <c r="U10" t="s">
-        <v>137</v>
-      </c>
-      <c r="V10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" t="s">
-        <v>141</v>
-      </c>
-      <c r="I11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" t="s">
-        <v>131</v>
-      </c>
-      <c r="N11" t="s">
-        <v>142</v>
-      </c>
-      <c r="O11" t="s">
-        <v>143</v>
-      </c>
-      <c r="P11" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>37</v>
-      </c>
-      <c r="R11" t="s">
-        <v>93</v>
-      </c>
-      <c r="S11" t="s">
-        <v>145</v>
-      </c>
-      <c r="T11" t="s">
-        <v>146</v>
-      </c>
-      <c r="U11" t="s">
-        <v>147</v>
-      </c>
-      <c r="V11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
-      <c r="A12" t="s">
-        <v>148</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>149</v>
-      </c>
-      <c r="F12" t="s">
-        <v>150</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" t="s">
-        <v>151</v>
-      </c>
-      <c r="I12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" t="s">
-        <v>131</v>
-      </c>
-      <c r="N12" t="s">
-        <v>152</v>
-      </c>
-      <c r="O12" t="s">
-        <v>153</v>
-      </c>
-      <c r="P12" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>37</v>
-      </c>
-      <c r="R12" t="s">
-        <v>38</v>
-      </c>
-      <c r="S12" t="s">
-        <v>155</v>
-      </c>
-      <c r="T12" t="s">
-        <v>156</v>
-      </c>
-      <c r="U12" t="s">
-        <v>157</v>
-      </c>
-      <c r="V12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
-      <c r="A13" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" t="s">
-        <v>160</v>
-      </c>
-      <c r="G13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" t="s">
-        <v>161</v>
-      </c>
-      <c r="I13" t="s">
-        <v>49</v>
-      </c>
-      <c r="J13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" t="s">
-        <v>33</v>
-      </c>
-      <c r="M13" t="s">
-        <v>131</v>
-      </c>
-      <c r="N13" t="s">
-        <v>162</v>
-      </c>
-      <c r="O13" t="s">
-        <v>163</v>
-      </c>
-      <c r="P13" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>69</v>
-      </c>
-      <c r="R13" t="s">
-        <v>54</v>
-      </c>
-      <c r="S13" t="s">
-        <v>165</v>
-      </c>
-      <c r="T13" t="s">
-        <v>166</v>
-      </c>
-      <c r="U13" t="s">
-        <v>167</v>
-      </c>
-      <c r="V13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
-      <c r="A14" t="s">
-        <v>168</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>169</v>
-      </c>
-      <c r="F14" t="s">
-        <v>170</v>
-      </c>
-      <c r="G14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" t="s">
-        <v>171</v>
-      </c>
-      <c r="I14" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L14" t="s">
-        <v>33</v>
-      </c>
-      <c r="M14" t="s">
-        <v>31</v>
-      </c>
-      <c r="N14" t="s">
-        <v>172</v>
-      </c>
-      <c r="O14" t="s">
-        <v>173</v>
-      </c>
-      <c r="P14" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>37</v>
-      </c>
-      <c r="R14" t="s">
-        <v>70</v>
-      </c>
-      <c r="S14" t="s">
-        <v>175</v>
-      </c>
-      <c r="T14" t="s">
-        <v>176</v>
-      </c>
-      <c r="U14" t="s">
-        <v>177</v>
-      </c>
-      <c r="V14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
-      <c r="A15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>179</v>
-      </c>
-      <c r="F15" t="s">
-        <v>180</v>
-      </c>
-      <c r="G15" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" t="s">
-        <v>181</v>
-      </c>
-      <c r="I15" t="s">
-        <v>49</v>
-      </c>
-      <c r="J15" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" t="s">
-        <v>50</v>
-      </c>
-      <c r="L15" t="s">
-        <v>33</v>
-      </c>
-      <c r="M15" t="s">
-        <v>131</v>
-      </c>
-      <c r="N15" t="s">
-        <v>182</v>
-      </c>
-      <c r="O15" t="s">
-        <v>183</v>
-      </c>
-      <c r="P15" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>37</v>
-      </c>
-      <c r="R15" t="s">
-        <v>82</v>
-      </c>
-      <c r="S15" t="s">
-        <v>185</v>
-      </c>
-      <c r="T15" t="s">
-        <v>186</v>
-      </c>
-      <c r="U15" t="s">
-        <v>187</v>
-      </c>
-      <c r="V15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
-      <c r="A16" t="s">
-        <v>188</v>
-      </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>189</v>
-      </c>
-      <c r="F16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" t="s">
-        <v>191</v>
-      </c>
-      <c r="I16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J16" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" t="s">
-        <v>50</v>
-      </c>
-      <c r="L16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16" t="s">
-        <v>131</v>
-      </c>
-      <c r="N16" t="s">
-        <v>192</v>
-      </c>
-      <c r="O16" t="s">
-        <v>193</v>
-      </c>
-      <c r="P16" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>69</v>
-      </c>
-      <c r="R16" t="s">
-        <v>93</v>
-      </c>
-      <c r="S16" t="s">
-        <v>195</v>
-      </c>
-      <c r="T16" t="s">
-        <v>196</v>
-      </c>
-      <c r="U16" t="s">
-        <v>197</v>
-      </c>
-      <c r="V16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
-      <c r="A17" t="s">
-        <v>198</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>199</v>
-      </c>
-      <c r="F17" t="s">
-        <v>200</v>
-      </c>
-      <c r="G17" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" t="s">
-        <v>201</v>
-      </c>
-      <c r="I17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" t="s">
-        <v>32</v>
-      </c>
-      <c r="L17" t="s">
-        <v>33</v>
-      </c>
-      <c r="M17" t="s">
-        <v>131</v>
-      </c>
-      <c r="N17" t="s">
-        <v>202</v>
-      </c>
-      <c r="O17" t="s">
-        <v>203</v>
-      </c>
-      <c r="P17" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>37</v>
-      </c>
-      <c r="R17" t="s">
-        <v>38</v>
-      </c>
-      <c r="S17" t="s">
-        <v>205</v>
-      </c>
-      <c r="T17" t="s">
-        <v>206</v>
-      </c>
-      <c r="U17" t="s">
-        <v>207</v>
-      </c>
-      <c r="V17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
-      <c r="A18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>209</v>
-      </c>
-      <c r="F18" t="s">
-        <v>210</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
-      </c>
-      <c r="H18" t="s">
-        <v>211</v>
-      </c>
-      <c r="I18" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" t="s">
-        <v>50</v>
-      </c>
-      <c r="L18" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18" t="s">
-        <v>131</v>
-      </c>
-      <c r="N18" t="s">
-        <v>212</v>
-      </c>
-      <c r="O18" t="s">
-        <v>213</v>
-      </c>
-      <c r="P18" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>37</v>
-      </c>
-      <c r="R18" t="s">
-        <v>54</v>
-      </c>
-      <c r="S18" t="s">
-        <v>215</v>
-      </c>
-      <c r="T18" t="s">
-        <v>216</v>
-      </c>
-      <c r="U18" t="s">
-        <v>217</v>
-      </c>
-      <c r="V18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
-      <c r="A19" t="s">
-        <v>218</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" t="s">
-        <v>219</v>
-      </c>
-      <c r="F19" t="s">
-        <v>220</v>
-      </c>
-      <c r="G19" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" t="s">
-        <v>221</v>
-      </c>
-      <c r="I19" t="s">
-        <v>49</v>
-      </c>
-      <c r="J19" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" t="s">
-        <v>50</v>
-      </c>
-      <c r="L19" t="s">
-        <v>33</v>
-      </c>
-      <c r="M19" t="s">
-        <v>131</v>
-      </c>
-      <c r="N19" t="s">
-        <v>222</v>
-      </c>
-      <c r="O19" t="s">
-        <v>223</v>
-      </c>
-      <c r="P19" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>69</v>
-      </c>
-      <c r="R19" t="s">
-        <v>70</v>
-      </c>
-      <c r="S19" t="s">
-        <v>225</v>
-      </c>
-      <c r="T19" t="s">
-        <v>226</v>
-      </c>
-      <c r="U19" t="s">
-        <v>227</v>
-      </c>
-      <c r="V19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
-      <c r="A20" t="s">
-        <v>228</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" t="s">
-        <v>229</v>
-      </c>
-      <c r="F20" t="s">
-        <v>230</v>
-      </c>
-      <c r="G20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" t="s">
-        <v>231</v>
-      </c>
-      <c r="I20" t="s">
-        <v>30</v>
-      </c>
-      <c r="J20" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M20" t="s">
-        <v>31</v>
-      </c>
-      <c r="N20" t="s">
-        <v>232</v>
-      </c>
-      <c r="O20" t="s">
-        <v>233</v>
-      </c>
-      <c r="P20" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>37</v>
-      </c>
-      <c r="R20" t="s">
-        <v>82</v>
-      </c>
-      <c r="S20" t="s">
-        <v>235</v>
-      </c>
-      <c r="T20" t="s">
-        <v>236</v>
-      </c>
-      <c r="U20" t="s">
-        <v>237</v>
-      </c>
-      <c r="V20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
-      <c r="A21" t="s">
-        <v>238</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" t="s">
-        <v>239</v>
-      </c>
-      <c r="F21" t="s">
-        <v>240</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
-      </c>
-      <c r="H21" t="s">
-        <v>241</v>
-      </c>
-      <c r="I21" t="s">
-        <v>49</v>
-      </c>
-      <c r="J21" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" t="s">
-        <v>50</v>
-      </c>
-      <c r="L21" t="s">
-        <v>33</v>
-      </c>
-      <c r="M21" t="s">
-        <v>131</v>
-      </c>
-      <c r="N21" t="s">
-        <v>242</v>
-      </c>
-      <c r="O21" t="s">
-        <v>243</v>
-      </c>
-      <c r="P21" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>37</v>
-      </c>
-      <c r="R21" t="s">
-        <v>93</v>
-      </c>
-      <c r="S21" t="s">
-        <v>245</v>
-      </c>
-      <c r="T21" t="s">
-        <v>246</v>
-      </c>
-      <c r="U21" t="s">
-        <v>247</v>
-      </c>
-      <c r="V21" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V21">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/安全体检报告/风险清单/资产清单.xlsx
+++ b/安全体检报告/风险清单/资产清单.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="245">
   <si>
     <t>IP地址</t>
   </si>
@@ -104,9 +104,6 @@
     <t>办公网络</t>
   </si>
   <si>
-    <t>业务系统1</t>
-  </si>
-  <si>
     <t>未知</t>
   </si>
   <si>
@@ -167,9 +164,6 @@
     <t>192.168.213.156</t>
   </si>
   <si>
-    <t>业务系统2</t>
-  </si>
-  <si>
     <t>01:03:07:42:03:62</t>
   </si>
   <si>
@@ -215,9 +209,6 @@
     <t>192.168.76.20</t>
   </si>
   <si>
-    <t>业务系统3</t>
-  </si>
-  <si>
     <t>02:06:0E:43:06:61</t>
   </si>
   <si>
@@ -260,9 +251,6 @@
     <t>192.168.200.33</t>
   </si>
   <si>
-    <t>业务系统4</t>
-  </si>
-  <si>
     <t>03:09:15:44:09:60</t>
   </si>
   <si>
@@ -296,9 +284,6 @@
     <t>192.168.200.22</t>
   </si>
   <si>
-    <t>业务系统5</t>
-  </si>
-  <si>
     <t>04:0C:1C:45:0C:5F</t>
   </si>
   <si>
@@ -332,9 +317,6 @@
     <t>192.168.100.205</t>
   </si>
   <si>
-    <t>业务系统6</t>
-  </si>
-  <si>
     <t>05:0F:23:46:0F:5E</t>
   </si>
   <si>
@@ -725,9 +707,6 @@
     <t>172.16.88.30</t>
   </si>
   <si>
-    <t>业务系统7</t>
-  </si>
-  <si>
     <t>12:36:7E:53:36:51</t>
   </si>
   <si>
@@ -756,9 +735,6 @@
   </si>
   <si>
     <t>192.168.1.100</t>
-  </si>
-  <si>
-    <t>业务系统8</t>
   </si>
   <si>
     <t>13:39:85:54:39:50</t>
@@ -1834,1417 +1810,1377 @@
       <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3"/>
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>32</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>33</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
         <v>34</v>
       </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>35</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>36</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>38</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>39</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>40</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>41</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>42</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4"/>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
         <v>46</v>
       </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>47</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>48</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>49</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>50</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>51</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" t="s">
         <v>52</v>
       </c>
-      <c r="K4" t="s">
+      <c r="O4" t="s">
         <v>53</v>
       </c>
-      <c r="L4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="P4" t="s">
         <v>54</v>
       </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R4" t="s">
         <v>55</v>
       </c>
-      <c r="P4" t="s">
+      <c r="S4" t="s">
         <v>56</v>
       </c>
-      <c r="Q4" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" t="s">
+      <c r="T4" t="s">
         <v>57</v>
       </c>
-      <c r="S4" t="s">
+      <c r="U4" t="s">
         <v>58</v>
       </c>
-      <c r="T4" t="s">
-        <v>59</v>
-      </c>
-      <c r="U4" t="s">
-        <v>60</v>
-      </c>
       <c r="V4" t="s">
+        <v>42</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5"/>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" t="s">
         <v>62</v>
       </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>63</v>
       </c>
-      <c r="F5" t="s">
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" t="s">
         <v>64</v>
       </c>
-      <c r="G5" t="s">
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" t="s">
         <v>65</v>
       </c>
-      <c r="H5" t="s">
+      <c r="O5" t="s">
         <v>66</v>
       </c>
-      <c r="I5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="P5" t="s">
         <v>67</v>
       </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="Q5" t="s">
         <v>68</v>
       </c>
-      <c r="O5" t="s">
+      <c r="R5" t="s">
         <v>69</v>
       </c>
-      <c r="P5" t="s">
+      <c r="S5" t="s">
         <v>70</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="T5" t="s">
         <v>71</v>
       </c>
-      <c r="R5" t="s">
+      <c r="U5" t="s">
         <v>72</v>
       </c>
-      <c r="S5" t="s">
-        <v>73</v>
-      </c>
-      <c r="T5" t="s">
-        <v>74</v>
-      </c>
-      <c r="U5" t="s">
-        <v>75</v>
-      </c>
       <c r="V5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W5" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6"/>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" t="s">
         <v>77</v>
       </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="O6" t="s">
         <v>78</v>
       </c>
-      <c r="F6" t="s">
+      <c r="P6" t="s">
         <v>79</v>
       </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="Q6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6" t="s">
         <v>80</v>
       </c>
-      <c r="I6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" t="s">
-        <v>32</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="S6" t="s">
         <v>81</v>
       </c>
-      <c r="O6" t="s">
+      <c r="T6" t="s">
         <v>82</v>
       </c>
-      <c r="P6" t="s">
+      <c r="U6" t="s">
         <v>83</v>
       </c>
-      <c r="Q6" t="s">
-        <v>38</v>
-      </c>
-      <c r="R6" t="s">
-        <v>84</v>
-      </c>
-      <c r="S6" t="s">
-        <v>85</v>
-      </c>
-      <c r="T6" t="s">
-        <v>86</v>
-      </c>
-      <c r="U6" t="s">
-        <v>87</v>
-      </c>
       <c r="V6" t="s">
+        <v>42</v>
+      </c>
+      <c r="W6" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7"/>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" t="s">
+        <v>88</v>
+      </c>
+      <c r="O7" t="s">
         <v>89</v>
       </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="P7" t="s">
         <v>90</v>
       </c>
-      <c r="F7" t="s">
+      <c r="Q7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R7" t="s">
         <v>91</v>
       </c>
-      <c r="G7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="S7" t="s">
         <v>92</v>
       </c>
-      <c r="I7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="T7" t="s">
         <v>93</v>
       </c>
-      <c r="O7" t="s">
+      <c r="U7" t="s">
         <v>94</v>
       </c>
-      <c r="P7" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>38</v>
-      </c>
-      <c r="R7" t="s">
-        <v>96</v>
-      </c>
-      <c r="S7" t="s">
-        <v>97</v>
-      </c>
-      <c r="T7" t="s">
-        <v>98</v>
-      </c>
-      <c r="U7" t="s">
-        <v>99</v>
-      </c>
       <c r="V7" t="s">
+        <v>42</v>
+      </c>
+      <c r="W7" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8"/>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" t="s">
+        <v>99</v>
+      </c>
+      <c r="O8" t="s">
+        <v>100</v>
+      </c>
+      <c r="P8" t="s">
         <v>101</v>
       </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="Q8" t="s">
+        <v>68</v>
+      </c>
+      <c r="R8" t="s">
+        <v>38</v>
+      </c>
+      <c r="S8" t="s">
         <v>102</v>
       </c>
-      <c r="F8" t="s">
+      <c r="T8" t="s">
         <v>103</v>
       </c>
-      <c r="G8" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="U8" t="s">
         <v>104</v>
       </c>
-      <c r="I8" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" t="s">
-        <v>105</v>
-      </c>
-      <c r="O8" t="s">
-        <v>106</v>
-      </c>
-      <c r="P8" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>71</v>
-      </c>
-      <c r="R8" t="s">
-        <v>39</v>
-      </c>
-      <c r="S8" t="s">
-        <v>108</v>
-      </c>
-      <c r="T8" t="s">
-        <v>109</v>
-      </c>
-      <c r="U8" t="s">
-        <v>110</v>
-      </c>
       <c r="V8" t="s">
+        <v>42</v>
+      </c>
+      <c r="W8" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9"/>
+      <c r="D9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
       <c r="E9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" t="s">
+        <v>109</v>
+      </c>
+      <c r="O9" t="s">
+        <v>110</v>
+      </c>
+      <c r="P9" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R9" t="s">
+        <v>55</v>
+      </c>
+      <c r="S9" t="s">
         <v>112</v>
       </c>
-      <c r="F9" t="s">
+      <c r="T9" t="s">
         <v>113</v>
       </c>
-      <c r="G9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="U9" t="s">
         <v>114</v>
       </c>
-      <c r="I9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" t="s">
-        <v>67</v>
-      </c>
-      <c r="M9" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" t="s">
-        <v>115</v>
-      </c>
-      <c r="O9" t="s">
-        <v>116</v>
-      </c>
-      <c r="P9" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R9" t="s">
-        <v>57</v>
-      </c>
-      <c r="S9" t="s">
-        <v>118</v>
-      </c>
-      <c r="T9" t="s">
-        <v>119</v>
-      </c>
-      <c r="U9" t="s">
-        <v>120</v>
-      </c>
       <c r="V9" t="s">
+        <v>42</v>
+      </c>
+      <c r="W9" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
+      <c r="C10"/>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" t="s">
+        <v>120</v>
+      </c>
+      <c r="P10" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>37</v>
+      </c>
+      <c r="R10" t="s">
+        <v>69</v>
+      </c>
+      <c r="S10" t="s">
         <v>122</v>
       </c>
-      <c r="F10" t="s">
+      <c r="T10" t="s">
         <v>123</v>
       </c>
-      <c r="G10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="U10" t="s">
         <v>124</v>
       </c>
-      <c r="I10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" t="s">
-        <v>52</v>
-      </c>
-      <c r="K10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" t="s">
-        <v>32</v>
-      </c>
-      <c r="N10" t="s">
-        <v>125</v>
-      </c>
-      <c r="O10" t="s">
-        <v>126</v>
-      </c>
-      <c r="P10" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>38</v>
-      </c>
-      <c r="R10" t="s">
-        <v>72</v>
-      </c>
-      <c r="S10" t="s">
-        <v>128</v>
-      </c>
-      <c r="T10" t="s">
-        <v>129</v>
-      </c>
-      <c r="U10" t="s">
-        <v>130</v>
-      </c>
       <c r="V10" t="s">
+        <v>42</v>
+      </c>
+      <c r="W10" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11"/>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G11" t="s">
         <v>62</v>
       </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="H11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" t="s">
+        <v>129</v>
+      </c>
+      <c r="O11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P11" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>68</v>
+      </c>
+      <c r="R11" t="s">
+        <v>80</v>
+      </c>
+      <c r="S11" t="s">
         <v>132</v>
       </c>
-      <c r="F11" t="s">
+      <c r="T11" t="s">
         <v>133</v>
       </c>
-      <c r="G11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="U11" t="s">
         <v>134</v>
       </c>
-      <c r="I11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" t="s">
-        <v>52</v>
-      </c>
-      <c r="N11" t="s">
-        <v>135</v>
-      </c>
-      <c r="O11" t="s">
-        <v>136</v>
-      </c>
-      <c r="P11" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>71</v>
-      </c>
-      <c r="R11" t="s">
-        <v>84</v>
-      </c>
-      <c r="S11" t="s">
-        <v>138</v>
-      </c>
-      <c r="T11" t="s">
-        <v>139</v>
-      </c>
-      <c r="U11" t="s">
-        <v>140</v>
-      </c>
       <c r="V11" t="s">
+        <v>42</v>
+      </c>
+      <c r="W11" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
-        <v>77</v>
-      </c>
+      <c r="C12"/>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12" t="s">
+        <v>139</v>
+      </c>
+      <c r="O12" t="s">
+        <v>140</v>
+      </c>
+      <c r="P12" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>37</v>
+      </c>
+      <c r="R12" t="s">
+        <v>91</v>
+      </c>
+      <c r="S12" t="s">
         <v>142</v>
       </c>
-      <c r="F12" t="s">
+      <c r="T12" t="s">
         <v>143</v>
       </c>
-      <c r="G12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="U12" t="s">
         <v>144</v>
       </c>
-      <c r="I12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L12" t="s">
-        <v>34</v>
-      </c>
-      <c r="M12" t="s">
-        <v>52</v>
-      </c>
-      <c r="N12" t="s">
-        <v>145</v>
-      </c>
-      <c r="O12" t="s">
-        <v>146</v>
-      </c>
-      <c r="P12" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>38</v>
-      </c>
-      <c r="R12" t="s">
-        <v>96</v>
-      </c>
-      <c r="S12" t="s">
-        <v>148</v>
-      </c>
-      <c r="T12" t="s">
-        <v>149</v>
-      </c>
-      <c r="U12" t="s">
-        <v>150</v>
-      </c>
       <c r="V12" t="s">
+        <v>42</v>
+      </c>
+      <c r="W12" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" t="s">
-        <v>89</v>
-      </c>
+      <c r="C13"/>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>64</v>
+      </c>
+      <c r="M13" t="s">
+        <v>50</v>
+      </c>
+      <c r="N13" t="s">
+        <v>149</v>
+      </c>
+      <c r="O13" t="s">
+        <v>150</v>
+      </c>
+      <c r="P13" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>37</v>
+      </c>
+      <c r="R13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S13" t="s">
         <v>152</v>
       </c>
-      <c r="F13" t="s">
+      <c r="T13" t="s">
         <v>153</v>
       </c>
-      <c r="G13" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="U13" t="s">
         <v>154</v>
       </c>
-      <c r="I13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K13" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13" t="s">
-        <v>52</v>
-      </c>
-      <c r="N13" t="s">
-        <v>155</v>
-      </c>
-      <c r="O13" t="s">
-        <v>156</v>
-      </c>
-      <c r="P13" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>38</v>
-      </c>
-      <c r="R13" t="s">
-        <v>39</v>
-      </c>
-      <c r="S13" t="s">
-        <v>158</v>
-      </c>
-      <c r="T13" t="s">
-        <v>159</v>
-      </c>
-      <c r="U13" t="s">
-        <v>160</v>
-      </c>
       <c r="V13" t="s">
+        <v>42</v>
+      </c>
+      <c r="W13" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
+      <c r="C14"/>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J14" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" t="s">
+        <v>50</v>
+      </c>
+      <c r="N14" t="s">
+        <v>159</v>
+      </c>
+      <c r="O14" t="s">
+        <v>160</v>
+      </c>
+      <c r="P14" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>68</v>
+      </c>
+      <c r="R14" t="s">
+        <v>55</v>
+      </c>
+      <c r="S14" t="s">
         <v>162</v>
       </c>
-      <c r="F14" t="s">
+      <c r="T14" t="s">
         <v>163</v>
       </c>
-      <c r="G14" t="s">
-        <v>65</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="U14" t="s">
         <v>164</v>
       </c>
-      <c r="I14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14" t="s">
-        <v>53</v>
-      </c>
-      <c r="L14" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N14" t="s">
-        <v>165</v>
-      </c>
-      <c r="O14" t="s">
-        <v>166</v>
-      </c>
-      <c r="P14" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>71</v>
-      </c>
-      <c r="R14" t="s">
-        <v>57</v>
-      </c>
-      <c r="S14" t="s">
-        <v>168</v>
-      </c>
-      <c r="T14" t="s">
-        <v>169</v>
-      </c>
-      <c r="U14" t="s">
-        <v>170</v>
-      </c>
       <c r="V14" t="s">
+        <v>42</v>
+      </c>
+      <c r="W14" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15"/>
+      <c r="D15" t="s">
         <v>25</v>
       </c>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
       <c r="E15" t="s">
+        <v>166</v>
+      </c>
+      <c r="F15" t="s">
+        <v>167</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" t="s">
+        <v>51</v>
+      </c>
+      <c r="L15" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" t="s">
+        <v>169</v>
+      </c>
+      <c r="O15" t="s">
+        <v>170</v>
+      </c>
+      <c r="P15" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>37</v>
+      </c>
+      <c r="R15" t="s">
+        <v>69</v>
+      </c>
+      <c r="S15" t="s">
         <v>172</v>
       </c>
-      <c r="F15" t="s">
+      <c r="T15" t="s">
         <v>173</v>
       </c>
-      <c r="G15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="U15" t="s">
         <v>174</v>
       </c>
-      <c r="I15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" t="s">
-        <v>175</v>
-      </c>
-      <c r="O15" t="s">
-        <v>176</v>
-      </c>
-      <c r="P15" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>38</v>
-      </c>
-      <c r="R15" t="s">
-        <v>72</v>
-      </c>
-      <c r="S15" t="s">
-        <v>178</v>
-      </c>
-      <c r="T15" t="s">
-        <v>179</v>
-      </c>
-      <c r="U15" t="s">
-        <v>180</v>
-      </c>
       <c r="V15" t="s">
+        <v>42</v>
+      </c>
+      <c r="W15" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
+      <c r="C16"/>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
+        <v>176</v>
+      </c>
+      <c r="F16" t="s">
+        <v>177</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" t="s">
+        <v>178</v>
+      </c>
+      <c r="I16" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L16" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N16" t="s">
+        <v>179</v>
+      </c>
+      <c r="O16" t="s">
+        <v>180</v>
+      </c>
+      <c r="P16" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" t="s">
+        <v>80</v>
+      </c>
+      <c r="S16" t="s">
         <v>182</v>
       </c>
-      <c r="F16" t="s">
+      <c r="T16" t="s">
         <v>183</v>
       </c>
-      <c r="G16" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="U16" t="s">
         <v>184</v>
       </c>
-      <c r="I16" t="s">
-        <v>51</v>
-      </c>
-      <c r="J16" t="s">
-        <v>52</v>
-      </c>
-      <c r="K16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" t="s">
-        <v>34</v>
-      </c>
-      <c r="M16" t="s">
-        <v>52</v>
-      </c>
-      <c r="N16" t="s">
-        <v>185</v>
-      </c>
-      <c r="O16" t="s">
-        <v>186</v>
-      </c>
-      <c r="P16" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>38</v>
-      </c>
-      <c r="R16" t="s">
-        <v>84</v>
-      </c>
-      <c r="S16" t="s">
-        <v>188</v>
-      </c>
-      <c r="T16" t="s">
-        <v>189</v>
-      </c>
-      <c r="U16" t="s">
-        <v>190</v>
-      </c>
       <c r="V16" t="s">
+        <v>42</v>
+      </c>
+      <c r="W16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:23">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17"/>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>186</v>
+      </c>
+      <c r="F17" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17" t="s">
         <v>62</v>
       </c>
-      <c r="D17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="H17" t="s">
+        <v>188</v>
+      </c>
+      <c r="I17" t="s">
+        <v>30</v>
+      </c>
+      <c r="J17" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" t="s">
+        <v>50</v>
+      </c>
+      <c r="N17" t="s">
+        <v>189</v>
+      </c>
+      <c r="O17" t="s">
+        <v>190</v>
+      </c>
+      <c r="P17" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>68</v>
+      </c>
+      <c r="R17" t="s">
+        <v>91</v>
+      </c>
+      <c r="S17" t="s">
         <v>192</v>
       </c>
-      <c r="F17" t="s">
+      <c r="T17" t="s">
         <v>193</v>
       </c>
-      <c r="G17" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="U17" t="s">
         <v>194</v>
       </c>
-      <c r="I17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" t="s">
-        <v>52</v>
-      </c>
-      <c r="K17" t="s">
-        <v>53</v>
-      </c>
-      <c r="L17" t="s">
-        <v>67</v>
-      </c>
-      <c r="M17" t="s">
-        <v>52</v>
-      </c>
-      <c r="N17" t="s">
-        <v>195</v>
-      </c>
-      <c r="O17" t="s">
-        <v>196</v>
-      </c>
-      <c r="P17" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>71</v>
-      </c>
-      <c r="R17" t="s">
-        <v>96</v>
-      </c>
-      <c r="S17" t="s">
-        <v>198</v>
-      </c>
-      <c r="T17" t="s">
-        <v>199</v>
-      </c>
-      <c r="U17" t="s">
-        <v>200</v>
-      </c>
       <c r="V17" t="s">
+        <v>42</v>
+      </c>
+      <c r="W17" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
+      <c r="C18"/>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F18" t="s">
+        <v>197</v>
+      </c>
+      <c r="G18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" t="s">
+        <v>198</v>
+      </c>
+      <c r="I18" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" t="s">
+        <v>50</v>
+      </c>
+      <c r="N18" t="s">
+        <v>199</v>
+      </c>
+      <c r="O18" t="s">
+        <v>200</v>
+      </c>
+      <c r="P18" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>37</v>
+      </c>
+      <c r="R18" t="s">
+        <v>38</v>
+      </c>
+      <c r="S18" t="s">
         <v>202</v>
       </c>
-      <c r="F18" t="s">
+      <c r="T18" t="s">
         <v>203</v>
       </c>
-      <c r="G18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="U18" t="s">
         <v>204</v>
       </c>
-      <c r="I18" t="s">
-        <v>51</v>
-      </c>
-      <c r="J18" t="s">
-        <v>52</v>
-      </c>
-      <c r="K18" t="s">
-        <v>33</v>
-      </c>
-      <c r="L18" t="s">
-        <v>34</v>
-      </c>
-      <c r="M18" t="s">
-        <v>52</v>
-      </c>
-      <c r="N18" t="s">
-        <v>205</v>
-      </c>
-      <c r="O18" t="s">
-        <v>206</v>
-      </c>
-      <c r="P18" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>38</v>
-      </c>
-      <c r="R18" t="s">
-        <v>39</v>
-      </c>
-      <c r="S18" t="s">
-        <v>208</v>
-      </c>
-      <c r="T18" t="s">
-        <v>209</v>
-      </c>
-      <c r="U18" t="s">
-        <v>210</v>
-      </c>
       <c r="V18" t="s">
+        <v>42</v>
+      </c>
+      <c r="W18" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="C19" t="s">
-        <v>89</v>
-      </c>
+      <c r="C19"/>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
+        <v>206</v>
+      </c>
+      <c r="F19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G19" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" t="s">
+        <v>208</v>
+      </c>
+      <c r="I19" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" t="s">
+        <v>51</v>
+      </c>
+      <c r="L19" t="s">
+        <v>33</v>
+      </c>
+      <c r="M19" t="s">
+        <v>50</v>
+      </c>
+      <c r="N19" t="s">
+        <v>209</v>
+      </c>
+      <c r="O19" t="s">
+        <v>210</v>
+      </c>
+      <c r="P19" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>37</v>
+      </c>
+      <c r="R19" t="s">
+        <v>55</v>
+      </c>
+      <c r="S19" t="s">
         <v>212</v>
       </c>
-      <c r="F19" t="s">
+      <c r="T19" t="s">
         <v>213</v>
       </c>
-      <c r="G19" t="s">
-        <v>49</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="U19" t="s">
         <v>214</v>
       </c>
-      <c r="I19" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" t="s">
-        <v>52</v>
-      </c>
-      <c r="K19" t="s">
-        <v>53</v>
-      </c>
-      <c r="L19" t="s">
-        <v>34</v>
-      </c>
-      <c r="M19" t="s">
-        <v>52</v>
-      </c>
-      <c r="N19" t="s">
-        <v>215</v>
-      </c>
-      <c r="O19" t="s">
-        <v>216</v>
-      </c>
-      <c r="P19" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>38</v>
-      </c>
-      <c r="R19" t="s">
-        <v>57</v>
-      </c>
-      <c r="S19" t="s">
-        <v>218</v>
-      </c>
-      <c r="T19" t="s">
-        <v>219</v>
-      </c>
-      <c r="U19" t="s">
-        <v>220</v>
-      </c>
       <c r="V19" t="s">
+        <v>42</v>
+      </c>
+      <c r="W19" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
       </c>
-      <c r="C20" t="s">
-        <v>101</v>
-      </c>
+      <c r="C20"/>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
+        <v>216</v>
+      </c>
+      <c r="F20" t="s">
+        <v>217</v>
+      </c>
+      <c r="G20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" t="s">
+        <v>218</v>
+      </c>
+      <c r="I20" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" t="s">
+        <v>51</v>
+      </c>
+      <c r="L20" t="s">
+        <v>33</v>
+      </c>
+      <c r="M20" t="s">
+        <v>50</v>
+      </c>
+      <c r="N20" t="s">
+        <v>219</v>
+      </c>
+      <c r="O20" t="s">
+        <v>220</v>
+      </c>
+      <c r="P20" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R20" t="s">
+        <v>69</v>
+      </c>
+      <c r="S20" t="s">
         <v>222</v>
       </c>
-      <c r="F20" t="s">
+      <c r="T20" t="s">
         <v>223</v>
       </c>
-      <c r="G20" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="U20" t="s">
         <v>224</v>
       </c>
-      <c r="I20" t="s">
-        <v>51</v>
-      </c>
-      <c r="J20" t="s">
-        <v>52</v>
-      </c>
-      <c r="K20" t="s">
-        <v>53</v>
-      </c>
-      <c r="L20" t="s">
-        <v>34</v>
-      </c>
-      <c r="M20" t="s">
-        <v>52</v>
-      </c>
-      <c r="N20" t="s">
-        <v>225</v>
-      </c>
-      <c r="O20" t="s">
-        <v>226</v>
-      </c>
-      <c r="P20" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>71</v>
-      </c>
-      <c r="R20" t="s">
-        <v>72</v>
-      </c>
-      <c r="S20" t="s">
-        <v>228</v>
-      </c>
-      <c r="T20" t="s">
-        <v>229</v>
-      </c>
-      <c r="U20" t="s">
-        <v>230</v>
-      </c>
       <c r="V20" t="s">
+        <v>42</v>
+      </c>
+      <c r="W20" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21"/>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" t="s">
+        <v>227</v>
+      </c>
+      <c r="G21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" t="s">
+        <v>228</v>
+      </c>
+      <c r="I21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" t="s">
+        <v>51</v>
+      </c>
+      <c r="L21" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" t="s">
+        <v>31</v>
+      </c>
+      <c r="N21" t="s">
+        <v>229</v>
+      </c>
+      <c r="O21" t="s">
+        <v>230</v>
+      </c>
+      <c r="P21" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>37</v>
+      </c>
+      <c r="R21" t="s">
+        <v>80</v>
+      </c>
+      <c r="S21" t="s">
         <v>232</v>
       </c>
-      <c r="D21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="T21" t="s">
         <v>233</v>
       </c>
-      <c r="F21" t="s">
+      <c r="U21" t="s">
         <v>234</v>
       </c>
-      <c r="G21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" t="s">
-        <v>235</v>
-      </c>
-      <c r="I21" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" t="s">
-        <v>32</v>
-      </c>
-      <c r="K21" t="s">
-        <v>53</v>
-      </c>
-      <c r="L21" t="s">
-        <v>67</v>
-      </c>
-      <c r="M21" t="s">
-        <v>32</v>
-      </c>
-      <c r="N21" t="s">
-        <v>236</v>
-      </c>
-      <c r="O21" t="s">
-        <v>237</v>
-      </c>
-      <c r="P21" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>38</v>
-      </c>
-      <c r="R21" t="s">
-        <v>84</v>
-      </c>
-      <c r="S21" t="s">
-        <v>239</v>
-      </c>
-      <c r="T21" t="s">
-        <v>240</v>
-      </c>
-      <c r="U21" t="s">
-        <v>241</v>
-      </c>
       <c r="V21" t="s">
+        <v>42</v>
+      </c>
+      <c r="W21" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:23">
       <c r="A22" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22"/>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>236</v>
+      </c>
+      <c r="F22" t="s">
+        <v>237</v>
+      </c>
+      <c r="G22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" t="s">
+        <v>238</v>
+      </c>
+      <c r="I22" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" t="s">
+        <v>50</v>
+      </c>
+      <c r="K22" t="s">
+        <v>51</v>
+      </c>
+      <c r="L22" t="s">
+        <v>33</v>
+      </c>
+      <c r="M22" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22" t="s">
+        <v>239</v>
+      </c>
+      <c r="O22" t="s">
+        <v>240</v>
+      </c>
+      <c r="P22" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>37</v>
+      </c>
+      <c r="R22" t="s">
+        <v>91</v>
+      </c>
+      <c r="S22" t="s">
+        <v>242</v>
+      </c>
+      <c r="T22" t="s">
         <v>243</v>
       </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="U22" t="s">
         <v>244</v>
       </c>
-      <c r="F22" t="s">
-        <v>245</v>
-      </c>
-      <c r="G22" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" t="s">
-        <v>246</v>
-      </c>
-      <c r="I22" t="s">
-        <v>51</v>
-      </c>
-      <c r="J22" t="s">
-        <v>52</v>
-      </c>
-      <c r="K22" t="s">
-        <v>53</v>
-      </c>
-      <c r="L22" t="s">
-        <v>34</v>
-      </c>
-      <c r="M22" t="s">
-        <v>52</v>
-      </c>
-      <c r="N22" t="s">
-        <v>247</v>
-      </c>
-      <c r="O22" t="s">
-        <v>248</v>
-      </c>
-      <c r="P22" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>38</v>
-      </c>
-      <c r="R22" t="s">
-        <v>96</v>
-      </c>
-      <c r="S22" t="s">
-        <v>250</v>
-      </c>
-      <c r="T22" t="s">
-        <v>251</v>
-      </c>
-      <c r="U22" t="s">
-        <v>252</v>
-      </c>
       <c r="V22" t="s">
+        <v>42</v>
+      </c>
+      <c r="W22" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
